--- a/aReport_card/2025_2026/Second_term/JSS2/Second_term_JSS2_Business_Studies.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS2/Second_term_JSS2_Business_Studies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47C6977-75BF-467E-B94F-17B3BC47D23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A295863-303B-42DA-A796-98DFBF8303B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,9 +38,6 @@
     <t>24001</t>
   </si>
   <si>
-    <t>ABDUL-RAHAMAN</t>
-  </si>
-  <si>
     <t>24002</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>24008</t>
+  </si>
+  <si>
+    <t>ABDULRAHMAN</t>
   </si>
 </sst>
 </file>
@@ -489,159 +489,159 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
